--- a/frontend/frontend testing/test_results/Frontend_UI_Test_Results.xlsx
+++ b/frontend/frontend testing/test_results/Frontend_UI_Test_Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend Test Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed Test Cases" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Frontend Test Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Detailed Test Cases" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -448,7 +448,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="63" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:10</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000</t>
+          <t>https://api-implant-developed-1.onrender.com</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="54" customWidth="1" min="3" max="3"/>
-    <col width="51" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.1</v>
+        <v>1.34</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5285,7 +5285,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5589,7 +5589,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:08</t>
+          <t>2026-07-28 09:57:43</t>
         </is>
       </c>
     </row>
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1047.42</v>
+        <v>9709.91</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
@@ -6378,16 +6378,16 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1033.08</v>
+        <v>9464.4</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:52</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
@@ -6416,16 +6416,16 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1045.4</v>
+        <v>8967.23</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Backend response: 38.7</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:52</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
@@ -6454,16 +6454,16 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1060.79</v>
+        <v>9764.83</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
@@ -6492,16 +6492,16 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1044.41</v>
+        <v>9211.93</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:52</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
@@ -6530,16 +6530,16 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>1043.39</v>
+        <v>8985.77</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Backend response: 38.7</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:52</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
@@ -6568,16 +6568,16 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>1044.41</v>
+        <v>9673.299999999999</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
@@ -6606,16 +6606,16 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1059.79</v>
+        <v>9764.65</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
@@ -6644,16 +6644,16 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>1044.41</v>
+        <v>9930.35</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
@@ -6682,16 +6682,16 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1058.79</v>
+        <v>7687.05</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Backend response: 38.7</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
@@ -6720,16 +6720,16 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>1056.42</v>
+        <v>9885.870000000001</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
@@ -6758,16 +6758,16 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>1057.42</v>
+        <v>9853.790000000001</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
@@ -6796,16 +6796,16 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>1058.79</v>
+        <v>9702.77</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
@@ -6834,16 +6834,16 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>1058.81</v>
+        <v>9599.48</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:52</t>
         </is>
       </c>
     </row>
@@ -6863,7 +6863,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
@@ -6872,16 +6872,16 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>1060.82</v>
+        <v>9366.620000000001</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:52</t>
         </is>
       </c>
     </row>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
@@ -6910,16 +6910,16 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1059.82</v>
+        <v>8995.870000000001</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Backend response: 38.7</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:52</t>
         </is>
       </c>
     </row>
@@ -6939,7 +6939,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
@@ -6948,16 +6948,16 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>1058.82</v>
+        <v>9869.639999999999</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -6977,7 +6977,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
@@ -6986,16 +6986,16 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>1057.81</v>
+        <v>9736.379999999999</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
@@ -7024,16 +7024,16 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>1055.42</v>
+        <v>9615.66</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:52</t>
         </is>
       </c>
     </row>
@@ -7053,7 +7053,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
@@ -7062,16 +7062,16 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1025.08</v>
+        <v>9947.370000000001</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
@@ -7100,16 +7100,16 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1036.42</v>
+        <v>8984.969999999999</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Backend response: 38.7</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:52</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
@@ -7138,16 +7138,16 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1049.8</v>
+        <v>10024.93</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
@@ -7176,16 +7176,16 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>1042.15</v>
+        <v>9268.74</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:52</t>
         </is>
       </c>
     </row>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
@@ -7214,16 +7214,16 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>1035.12</v>
+        <v>9332.950000000001</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:52</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
@@ -7252,16 +7252,16 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1025.75</v>
+        <v>6803.56</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Backend response: 38.7</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:50</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
@@ -7290,16 +7290,16 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1023.93</v>
+        <v>9478.700000000001</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:52</t>
         </is>
       </c>
     </row>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
@@ -7328,16 +7328,16 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>1019.77</v>
+        <v>9893.34</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
@@ -7366,16 +7366,16 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1017.77</v>
+        <v>9947.16</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
@@ -7404,16 +7404,16 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>1015.77</v>
+        <v>9615.389999999999</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:52</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
@@ -7442,16 +7442,16 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>1009.36</v>
+        <v>7810.24</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Backend response: 38.7</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
@@ -7480,16 +7480,16 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1013.77</v>
+        <v>9853.68</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
@@ -7518,16 +7518,16 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>1010.77</v>
+        <v>9992.35</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
@@ -7556,16 +7556,16 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>1019.79</v>
+        <v>9702.129999999999</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
@@ -7594,16 +7594,16 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1018.78</v>
+        <v>9951.41</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
@@ -7632,16 +7632,16 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1019.76</v>
+        <v>7008.44</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Backend response: 38.7</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:50</t>
         </is>
       </c>
     </row>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
@@ -7670,16 +7670,16 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1016.76</v>
+        <v>9708.9</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
@@ -7708,16 +7708,16 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>1014.78</v>
+        <v>9867.809999999999</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -7737,7 +7737,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
@@ -7746,16 +7746,16 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>1013.77</v>
+        <v>9668.450000000001</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
@@ -7784,16 +7784,16 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>1012.77</v>
+        <v>9849.209999999999</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
@@ -7822,16 +7822,16 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1010.77</v>
+        <v>9845.17</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Validated (ReadTimeout)</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:53</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
@@ -7860,16 +7860,16 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>1010.64</v>
+        <v>397.15</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Backend response: 38.7</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:10</t>
+          <t>2026-07-28 09:57:50</t>
         </is>
       </c>
     </row>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
@@ -7898,16 +7898,16 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1008.64</v>
+        <v>288.08</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Backend response: 38.7</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:10</t>
+          <t>2026-07-28 09:57:50</t>
         </is>
       </c>
     </row>
@@ -7927,7 +7927,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
@@ -7936,16 +7936,16 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>1012.3</v>
+        <v>331.46</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Backend response: 38.7</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:10</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
@@ -7974,16 +7974,16 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>1011.3</v>
+        <v>527.0599999999999</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Backend response: 38.7</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:10</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000/predict</t>
+          <t>https://api-implant-developed-1.onrender.com/predict</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
@@ -8012,16 +8012,16 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1008.29</v>
+        <v>514.65</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Validated (ConnectTimeout)</t>
+          <t>Backend response: 38.7</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:10</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8287,7 +8287,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8325,7 +8325,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8363,7 +8363,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8401,7 +8401,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8515,7 +8515,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8553,7 +8553,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8705,7 +8705,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8857,7 +8857,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -8971,7 +8971,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9009,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9047,7 +9047,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9085,7 +9085,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9199,7 +9199,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9389,7 +9389,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9693,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9731,7 +9731,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9807,7 +9807,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -9997,7 +9997,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10035,7 +10035,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10111,7 +10111,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10225,7 +10225,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10301,7 +10301,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10339,7 +10339,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10377,7 +10377,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10453,7 +10453,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10529,7 +10529,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10605,7 +10605,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10643,7 +10643,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10757,7 +10757,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10795,7 +10795,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10833,7 +10833,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10871,7 +10871,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10947,7 +10947,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -10985,7 +10985,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11023,7 +11023,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11061,7 +11061,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11099,7 +11099,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11137,7 +11137,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11175,7 +11175,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11213,7 +11213,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11289,7 +11289,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11365,7 +11365,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11441,7 +11441,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11517,7 +11517,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11593,7 +11593,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11631,7 +11631,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11707,7 +11707,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11745,7 +11745,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11783,7 +11783,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11821,7 +11821,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11897,7 +11897,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -11973,7 +11973,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
@@ -12011,7 +12011,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>2026-07-27 22:38:09</t>
+          <t>2026-07-28 09:57:51</t>
         </is>
       </c>
     </row>
